--- a/이용매뉴얼/관리자-이용매뉴얼.xlsx
+++ b/이용매뉴얼/관리자-이용매뉴얼.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="115">
   <si>
     <t>관리자 이용 매뉴얼  |  비젠 회계관리 시스템 v1.0 (2026-10-01)</t>
   </si>
@@ -326,7 +326,7 @@
     <t>근속·생일 자동계산</t>
   </si>
   <si>
-    <t>6 · 세금·보고서</t>
+    <t>6 · 세금·보고서·휴지통</t>
   </si>
   <si>
     <t>세금관리</t>
@@ -349,6 +349,17 @@
   </si>
   <si>
     <t>사이드바는 인쇄 제외, 임원 보고용</t>
+  </si>
+  <si>
+    <t>휴지통 ★</t>
+  </si>
+  <si>
+    <r>
+      <t>관리 → 휴지통 → 장부·프로젝트 탭 → [복원]·[영구삭제]</t>
+    </r>
+  </si>
+  <si>
+    <t>삭제 버튼은 전부 휴지통 이동, 영구삭제는 되돌릴 수 없음</t>
   </si>
   <si>
     <t>규칙 · FAQ · 배포 체크리스트  |  관리자용</t>
@@ -1042,7 +1053,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1535,6 +1546,20 @@
       </c>
       <c r="D49" s="5" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>3</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1575,13 +1600,13 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B1" s="11"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B3" s="2"/>
     </row>
@@ -1590,15 +1615,15 @@
         <v>36</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1606,15 +1631,15 @@
         <v>39</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1622,107 +1647,107 @@
         <v>52</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1749,22 +1774,22 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
